--- a/artfynd/A 25093-2024 artfynd.xlsx
+++ b/artfynd/A 25093-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>132324997</v>
       </c>
       <c r="B2" t="n">
-        <v>99042</v>
+        <v>99112</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Arvid de Jong, Milad Avalinejad Bandari</t>
+          <t>Milad Avalinejad Bandari, Arvid de Jong</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132325005</v>
+        <v>132325002</v>
       </c>
       <c r="B3" t="n">
-        <v>99042</v>
+        <v>99112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550256</v>
+        <v>550229</v>
       </c>
       <c r="R3" t="n">
-        <v>6885697</v>
+        <v>6885650</v>
       </c>
       <c r="S3" t="n">
         <v>8</v>
@@ -856,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,10 +886,343 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Arvid de Jong, Milad Avalinejad Bandari</t>
+          <t>Milad Avalinejad Bandari, Arvid de Jong</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>C250246 Ljusdal NVI 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132325005</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hennan, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>550256</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6885697</v>
+      </c>
+      <c r="S4" t="n">
+        <v>8</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Milad Avalinejad Bandari</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Milad Avalinejad Bandari, Arvid de Jong</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>C250246 Ljusdal NVI 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>132325135</v>
+      </c>
+      <c r="B5" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hennan, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>550178</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6885353</v>
+      </c>
+      <c r="S5" t="n">
+        <v>8</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Milad Avalinejad Bandari</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Milad Avalinejad Bandari, Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>C250246 Ljusdal NVI 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>132325004</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99853</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222306</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Stjärnstarr</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Carex echinata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Murray</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hennan, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>550226</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6885659</v>
+      </c>
+      <c r="S6" t="n">
+        <v>8</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Milad Avalinejad Bandari</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Milad Avalinejad Bandari, Arvid de Jong</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>C250246 Ljusdal NVI 2025</t>
         </is>

--- a/artfynd/A 25093-2024 artfynd.xlsx
+++ b/artfynd/A 25093-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>C250246 Ljusdal NVI 2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132324997</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>C250246 Ljusdal NVI 2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132325002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>C250246 Ljusdal NVI 2025</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132325005</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
           <t>C250246 Ljusdal NVI 2025</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132325135</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,8 +1252,20 @@
           <t>C250246 Ljusdal NVI 2025</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132325004</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>